--- a/htk_files/results/Group_03_Analysis.xlsx
+++ b/htk_files/results/Group_03_Analysis.xlsx
@@ -8,28 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ceu365-my.sharepoint.com/personal/a_nava1_usp_ceu_es/Documents/Escritorio/Ingenieria Biomedica/2024-25/TFG/htk_files/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_1EF1916F5A4DAB608F0CC7F622D18F7752C49F4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FF86BA3-CB02-49B3-A39B-1C40572A7D07}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2CAF3C9689B67EC05B16FA8DEB71A46CF122E60D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB55445E-76E0-44A6-A731-A89D1300AEBE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="3_states" sheetId="4" r:id="rId1"/>
-    <sheet name="4_states" sheetId="5" r:id="rId2"/>
-    <sheet name="5_states" sheetId="6" r:id="rId3"/>
-    <sheet name="6_states" sheetId="7" r:id="rId4"/>
-    <sheet name="7_states" sheetId="8" r:id="rId5"/>
-    <sheet name="8_states" sheetId="9" r:id="rId6"/>
-    <sheet name="9_states" sheetId="10" r:id="rId7"/>
+    <sheet name="3_states" sheetId="7" r:id="rId1"/>
+    <sheet name="4_states" sheetId="8" r:id="rId2"/>
+    <sheet name="5_states" sheetId="9" r:id="rId3"/>
+    <sheet name="6_states" sheetId="10" r:id="rId4"/>
+    <sheet name="7_states" sheetId="11" r:id="rId5"/>
+    <sheet name="8_states" sheetId="12" r:id="rId6"/>
+    <sheet name="9_states" sheetId="13" r:id="rId7"/>
     <sheet name="10_states" sheetId="1" r:id="rId8"/>
     <sheet name="11_states" sheetId="2" r:id="rId9"/>
     <sheet name="12_states" sheetId="3" r:id="rId10"/>
+    <sheet name="13_states" sheetId="4" r:id="rId11"/>
+    <sheet name="14_states" sheetId="5" r:id="rId12"/>
+    <sheet name="15_states" sheetId="6" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="26">
   <si>
     <t>1_gaussians</t>
   </si>
@@ -468,7 +471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1573,12 +1576,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L12"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1610,162 +1613,237 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B2">
-        <v>43.33</v>
+        <v>46.67</v>
       </c>
       <c r="C2">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
       <c r="D2">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="E2">
-        <v>43.33</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>43.33</v>
       </c>
       <c r="H2">
-        <v>53.33</v>
+        <v>43.33</v>
       </c>
       <c r="I2">
-        <v>53.33</v>
+        <v>46.67</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>56.67</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="L2">
-        <v>50.33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="M2">
+        <v>46.67</v>
+      </c>
+      <c r="N2">
+        <v>46.67</v>
+      </c>
+      <c r="O2">
+        <v>43.33</v>
+      </c>
+      <c r="P2">
+        <v>40</v>
+      </c>
+      <c r="Q2">
+        <v>46.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>56.67</v>
+        <v>46.67</v>
       </c>
       <c r="C3">
-        <v>56.67</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>56.67</v>
       </c>
       <c r="E3">
-        <v>43.33</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="G3">
         <v>53.33</v>
       </c>
       <c r="H3">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>63.33</v>
+        <v>46.67</v>
       </c>
       <c r="J3">
-        <v>63.33</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>63.33</v>
+        <v>50</v>
       </c>
       <c r="L3">
-        <v>56.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>53.33</v>
+      </c>
+      <c r="M3">
+        <v>46.67</v>
+      </c>
+      <c r="N3">
+        <v>43.33</v>
+      </c>
+      <c r="O3">
+        <v>33.33</v>
+      </c>
+      <c r="P3">
+        <v>33.33</v>
+      </c>
+      <c r="Q3">
+        <v>47.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B4">
+        <v>53.33</v>
+      </c>
+      <c r="C4">
+        <v>53.33</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>43.33</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4">
+        <v>36.67</v>
+      </c>
+      <c r="H4">
         <v>33.33</v>
       </c>
-      <c r="C4">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>60</v>
-      </c>
-      <c r="E4">
+      <c r="I4">
         <v>33.33</v>
       </c>
-      <c r="F4">
-        <v>30</v>
-      </c>
-      <c r="G4">
-        <v>56.67</v>
-      </c>
-      <c r="H4">
-        <v>46.67</v>
-      </c>
-      <c r="I4">
-        <v>50</v>
-      </c>
       <c r="J4">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="K4">
-        <v>46.67</v>
+        <v>33.33</v>
       </c>
       <c r="L4">
-        <v>45.67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>36.67</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>43.33</v>
+      </c>
+      <c r="O4">
+        <v>46.67</v>
+      </c>
+      <c r="P4">
+        <v>46.67</v>
+      </c>
+      <c r="Q4">
+        <v>42.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B5">
-        <v>53.33</v>
+        <v>56.67</v>
       </c>
       <c r="C5">
-        <v>53.33</v>
+        <v>46.67</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>43.33</v>
       </c>
       <c r="E5">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="F5">
-        <v>63.33</v>
+        <v>50</v>
       </c>
       <c r="G5">
-        <v>63.33</v>
+        <v>56.67</v>
       </c>
       <c r="H5">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="I5">
-        <v>63.33</v>
+        <v>60</v>
       </c>
       <c r="J5">
-        <v>63.33</v>
+        <v>60</v>
       </c>
       <c r="K5">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="L5">
-        <v>59.33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>53.33</v>
+      </c>
+      <c r="M5">
+        <v>53.33</v>
+      </c>
+      <c r="N5">
+        <v>56.67</v>
+      </c>
+      <c r="O5">
+        <v>53.33</v>
+      </c>
+      <c r="P5">
+        <v>53.33</v>
+      </c>
+      <c r="Q5">
+        <v>52.67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1773,262 +1851,367 @@
         <v>46.67</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>36.67</v>
       </c>
       <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>40</v>
+      </c>
+      <c r="G6">
         <v>36.67</v>
       </c>
-      <c r="E6">
+      <c r="H6">
         <v>36.67</v>
       </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>30</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
       <c r="I6">
+        <v>36.67</v>
+      </c>
+      <c r="J6">
+        <v>40</v>
+      </c>
+      <c r="K6">
+        <v>43.33</v>
+      </c>
+      <c r="L6">
+        <v>43.33</v>
+      </c>
+      <c r="M6">
+        <v>43.33</v>
+      </c>
+      <c r="N6">
+        <v>36.67</v>
+      </c>
+      <c r="O6">
         <v>33.33</v>
       </c>
-      <c r="J6">
+      <c r="P6">
         <v>33.33</v>
       </c>
-      <c r="K6">
-        <v>30</v>
-      </c>
-      <c r="L6">
-        <v>35.67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <v>37.78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B7">
-        <v>36.67</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>43.33</v>
+        <v>53.33</v>
       </c>
       <c r="D7">
-        <v>46.67</v>
+        <v>56.67</v>
       </c>
       <c r="E7">
         <v>53.33</v>
       </c>
       <c r="F7">
-        <v>56.67</v>
+        <v>46.67</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="H7">
-        <v>56.67</v>
+        <v>63.33</v>
       </c>
       <c r="I7">
-        <v>63.33</v>
+        <v>60</v>
       </c>
       <c r="J7">
         <v>66.67</v>
       </c>
       <c r="K7">
+        <v>63.33</v>
+      </c>
+      <c r="L7">
         <v>66.67</v>
       </c>
-      <c r="L7">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7">
+        <v>66.67</v>
+      </c>
+      <c r="N7">
+        <v>70</v>
+      </c>
+      <c r="O7">
+        <v>70</v>
+      </c>
+      <c r="P7">
+        <v>73.33</v>
+      </c>
+      <c r="Q7">
+        <v>61.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>53.33</v>
+        <v>56.67</v>
       </c>
       <c r="C8">
-        <v>43.33</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>33.33</v>
+        <v>53.33</v>
       </c>
       <c r="E8">
-        <v>36.67</v>
+        <v>53.33</v>
       </c>
       <c r="F8">
-        <v>33.33</v>
+        <v>56.67</v>
       </c>
       <c r="G8">
-        <v>26.67</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>33.33</v>
+        <v>46.67</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>53.33</v>
       </c>
       <c r="J8">
-        <v>26.67</v>
+        <v>53.33</v>
       </c>
       <c r="K8">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="L8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>56.67</v>
+      </c>
+      <c r="M8">
+        <v>56.67</v>
+      </c>
+      <c r="N8">
+        <v>56.67</v>
+      </c>
+      <c r="O8">
+        <v>56.67</v>
+      </c>
+      <c r="P8">
+        <v>56.67</v>
+      </c>
+      <c r="Q8">
+        <v>53.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>56.67</v>
       </c>
       <c r="C9">
-        <v>26.67</v>
+        <v>43.33</v>
       </c>
       <c r="D9">
-        <v>23.33</v>
+        <v>46.67</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>46.67</v>
       </c>
       <c r="F9">
-        <v>33.33</v>
+        <v>46.67</v>
       </c>
       <c r="G9">
-        <v>36.67</v>
+        <v>46.67</v>
       </c>
       <c r="H9">
-        <v>43.33</v>
+        <v>53.33</v>
       </c>
       <c r="I9">
-        <v>43.33</v>
+        <v>60</v>
       </c>
       <c r="J9">
-        <v>46.67</v>
+        <v>60</v>
       </c>
       <c r="K9">
-        <v>50</v>
+        <v>56.67</v>
       </c>
       <c r="L9">
-        <v>37.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>53.33</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+      <c r="N9">
+        <v>50</v>
+      </c>
+      <c r="O9">
+        <v>50</v>
+      </c>
+      <c r="P9">
+        <v>50</v>
+      </c>
+      <c r="Q9">
+        <v>51.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B10">
-        <v>48.48</v>
+        <v>45.45</v>
       </c>
       <c r="C10">
         <v>45.45</v>
       </c>
       <c r="D10">
-        <v>36.36</v>
+        <v>42.42</v>
       </c>
       <c r="E10">
-        <v>60.61</v>
+        <v>48.48</v>
       </c>
       <c r="F10">
+        <v>48.48</v>
+      </c>
+      <c r="G10">
+        <v>57.58</v>
+      </c>
+      <c r="H10">
+        <v>57.58</v>
+      </c>
+      <c r="I10">
+        <v>51.52</v>
+      </c>
+      <c r="J10">
+        <v>54.55</v>
+      </c>
+      <c r="K10">
+        <v>54.55</v>
+      </c>
+      <c r="L10">
+        <v>63.64</v>
+      </c>
+      <c r="M10">
         <v>66.67</v>
       </c>
-      <c r="G10">
+      <c r="N10">
+        <v>66.67</v>
+      </c>
+      <c r="O10">
+        <v>69.7</v>
+      </c>
+      <c r="P10">
         <v>72.73</v>
       </c>
-      <c r="H10">
-        <v>72.73</v>
-      </c>
-      <c r="I10">
-        <v>69.7</v>
-      </c>
-      <c r="J10">
-        <v>66.67</v>
-      </c>
-      <c r="K10">
-        <v>63.64</v>
-      </c>
-      <c r="L10">
-        <v>60.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <v>56.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B11">
-        <v>54.55</v>
+        <v>51.52</v>
       </c>
       <c r="C11">
-        <v>45.45</v>
+        <v>48.48</v>
       </c>
       <c r="D11">
         <v>51.52</v>
       </c>
       <c r="E11">
-        <v>57.58</v>
+        <v>48.48</v>
       </c>
       <c r="F11">
-        <v>57.58</v>
+        <v>42.42</v>
       </c>
       <c r="G11">
-        <v>57.58</v>
+        <v>39.39</v>
       </c>
       <c r="H11">
-        <v>57.58</v>
+        <v>36.36</v>
       </c>
       <c r="I11">
-        <v>54.55</v>
+        <v>39.39</v>
       </c>
       <c r="J11">
-        <v>51.52</v>
+        <v>42.42</v>
       </c>
       <c r="K11">
-        <v>57.58</v>
+        <v>42.42</v>
       </c>
       <c r="L11">
-        <v>54.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>45.45</v>
+      </c>
+      <c r="M11">
+        <v>45.45</v>
+      </c>
+      <c r="N11">
+        <v>45.45</v>
+      </c>
+      <c r="O11">
+        <v>45.45</v>
+      </c>
+      <c r="P11">
+        <v>45.45</v>
+      </c>
+      <c r="Q11">
+        <v>44.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>46.64</v>
+        <v>51.03</v>
       </c>
       <c r="C12">
-        <v>47.09</v>
+        <v>46.06</v>
       </c>
       <c r="D12">
-        <v>44.46</v>
+        <v>49.06</v>
       </c>
       <c r="E12">
-        <v>46.15</v>
+        <v>46.36</v>
       </c>
       <c r="F12">
         <v>47.42</v>
       </c>
       <c r="G12">
-        <v>50.7</v>
+        <v>47.7</v>
       </c>
       <c r="H12">
-        <v>50.7</v>
+        <v>47.39</v>
       </c>
       <c r="I12">
-        <v>52.42</v>
+        <v>48.76</v>
       </c>
       <c r="J12">
-        <v>51.82</v>
+        <v>51.7</v>
       </c>
       <c r="K12">
-        <v>52.12</v>
+        <v>49.36</v>
       </c>
       <c r="L12">
-        <v>48.95</v>
+        <v>51.24</v>
+      </c>
+      <c r="M12">
+        <v>51.55</v>
+      </c>
+      <c r="N12">
+        <v>51.55</v>
+      </c>
+      <c r="O12">
+        <v>50.18</v>
+      </c>
+      <c r="P12">
+        <v>50.48</v>
+      </c>
+      <c r="Q12">
+        <v>49.32</v>
       </c>
     </row>
   </sheetData>
@@ -2036,7 +2219,650 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>43.33</v>
+      </c>
+      <c r="C2">
+        <v>53.33</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2">
+        <v>53.33</v>
+      </c>
+      <c r="H2">
+        <v>60</v>
+      </c>
+      <c r="I2">
+        <v>66.67</v>
+      </c>
+      <c r="J2">
+        <v>63.33</v>
+      </c>
+      <c r="K2">
+        <v>70</v>
+      </c>
+      <c r="L2">
+        <v>66.67</v>
+      </c>
+      <c r="M2">
+        <v>73.33</v>
+      </c>
+      <c r="N2">
+        <v>60</v>
+      </c>
+      <c r="O2">
+        <v>60</v>
+      </c>
+      <c r="P2">
+        <v>60</v>
+      </c>
+      <c r="Q2">
+        <v>59.33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3">
+        <v>53.33</v>
+      </c>
+      <c r="D3">
+        <v>53.33</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>53.33</v>
+      </c>
+      <c r="H3">
+        <v>56.67</v>
+      </c>
+      <c r="I3">
+        <v>56.67</v>
+      </c>
+      <c r="J3">
+        <v>56.67</v>
+      </c>
+      <c r="K3">
+        <v>53.33</v>
+      </c>
+      <c r="L3">
+        <v>50</v>
+      </c>
+      <c r="M3">
+        <v>53.33</v>
+      </c>
+      <c r="N3">
+        <v>56.67</v>
+      </c>
+      <c r="O3">
+        <v>60</v>
+      </c>
+      <c r="P3">
+        <v>53.33</v>
+      </c>
+      <c r="Q3">
+        <v>53.78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="C4">
+        <v>46.67</v>
+      </c>
+      <c r="D4">
+        <v>46.67</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="F4">
+        <v>53.33</v>
+      </c>
+      <c r="G4">
+        <v>56.67</v>
+      </c>
+      <c r="H4">
+        <v>53.33</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
+        <v>50</v>
+      </c>
+      <c r="K4">
+        <v>53.33</v>
+      </c>
+      <c r="L4">
+        <v>46.67</v>
+      </c>
+      <c r="M4">
+        <v>50</v>
+      </c>
+      <c r="N4">
+        <v>50</v>
+      </c>
+      <c r="O4">
+        <v>50</v>
+      </c>
+      <c r="P4">
+        <v>46.67</v>
+      </c>
+      <c r="Q4">
+        <v>49.56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>46.67</v>
+      </c>
+      <c r="C5">
+        <v>53.33</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>56.67</v>
+      </c>
+      <c r="I5">
+        <v>56.67</v>
+      </c>
+      <c r="J5">
+        <v>63.33</v>
+      </c>
+      <c r="K5">
+        <v>63.33</v>
+      </c>
+      <c r="L5">
+        <v>60</v>
+      </c>
+      <c r="M5">
+        <v>60</v>
+      </c>
+      <c r="N5">
+        <v>66.67</v>
+      </c>
+      <c r="O5">
+        <v>66.67</v>
+      </c>
+      <c r="P5">
+        <v>66.67</v>
+      </c>
+      <c r="Q5">
+        <v>59.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>43.33</v>
+      </c>
+      <c r="C6">
+        <v>46.67</v>
+      </c>
+      <c r="D6">
+        <v>43.33</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>43.33</v>
+      </c>
+      <c r="H6">
+        <v>36.67</v>
+      </c>
+      <c r="I6">
+        <v>40</v>
+      </c>
+      <c r="J6">
+        <v>33.33</v>
+      </c>
+      <c r="K6">
+        <v>33.33</v>
+      </c>
+      <c r="L6">
+        <v>33.33</v>
+      </c>
+      <c r="M6">
+        <v>36.67</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>36.67</v>
+      </c>
+      <c r="P6">
+        <v>36.67</v>
+      </c>
+      <c r="Q6">
+        <v>40.22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>43.33</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>56.67</v>
+      </c>
+      <c r="F7">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>46.67</v>
+      </c>
+      <c r="H7">
+        <v>46.67</v>
+      </c>
+      <c r="I7">
+        <v>43.33</v>
+      </c>
+      <c r="J7">
+        <v>53.33</v>
+      </c>
+      <c r="K7">
+        <v>53.33</v>
+      </c>
+      <c r="L7">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>50</v>
+      </c>
+      <c r="N7">
+        <v>53.33</v>
+      </c>
+      <c r="O7">
+        <v>53.33</v>
+      </c>
+      <c r="P7">
+        <v>53.33</v>
+      </c>
+      <c r="Q7">
+        <v>48.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>56.67</v>
+      </c>
+      <c r="D8">
+        <v>53.33</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>53.33</v>
+      </c>
+      <c r="H8">
+        <v>56.67</v>
+      </c>
+      <c r="I8">
+        <v>56.67</v>
+      </c>
+      <c r="J8">
+        <v>53.33</v>
+      </c>
+      <c r="K8">
+        <v>56.67</v>
+      </c>
+      <c r="L8">
+        <v>56.67</v>
+      </c>
+      <c r="M8">
+        <v>56.67</v>
+      </c>
+      <c r="N8">
+        <v>60</v>
+      </c>
+      <c r="O8">
+        <v>56.67</v>
+      </c>
+      <c r="P8">
+        <v>56.67</v>
+      </c>
+      <c r="Q8">
+        <v>55.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>53.33</v>
+      </c>
+      <c r="C9">
+        <v>43.33</v>
+      </c>
+      <c r="D9">
+        <v>46.67</v>
+      </c>
+      <c r="E9">
+        <v>46.67</v>
+      </c>
+      <c r="F9">
+        <v>46.67</v>
+      </c>
+      <c r="G9">
+        <v>43.33</v>
+      </c>
+      <c r="H9">
+        <v>56.67</v>
+      </c>
+      <c r="I9">
+        <v>63.33</v>
+      </c>
+      <c r="J9">
+        <v>60</v>
+      </c>
+      <c r="K9">
+        <v>63.33</v>
+      </c>
+      <c r="L9">
+        <v>53.33</v>
+      </c>
+      <c r="M9">
+        <v>53.33</v>
+      </c>
+      <c r="N9">
+        <v>53.33</v>
+      </c>
+      <c r="O9">
+        <v>50</v>
+      </c>
+      <c r="P9">
+        <v>50</v>
+      </c>
+      <c r="Q9">
+        <v>52.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>48.48</v>
+      </c>
+      <c r="C10">
+        <v>42.42</v>
+      </c>
+      <c r="D10">
+        <v>42.42</v>
+      </c>
+      <c r="E10">
+        <v>48.48</v>
+      </c>
+      <c r="F10">
+        <v>48.48</v>
+      </c>
+      <c r="G10">
+        <v>54.55</v>
+      </c>
+      <c r="H10">
+        <v>60.61</v>
+      </c>
+      <c r="I10">
+        <v>60.61</v>
+      </c>
+      <c r="J10">
+        <v>57.58</v>
+      </c>
+      <c r="K10">
+        <v>57.58</v>
+      </c>
+      <c r="L10">
+        <v>63.64</v>
+      </c>
+      <c r="M10">
+        <v>63.64</v>
+      </c>
+      <c r="N10">
+        <v>63.64</v>
+      </c>
+      <c r="O10">
+        <v>63.64</v>
+      </c>
+      <c r="P10">
+        <v>63.64</v>
+      </c>
+      <c r="Q10">
+        <v>55.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>51.52</v>
+      </c>
+      <c r="C11">
+        <v>48.48</v>
+      </c>
+      <c r="D11">
+        <v>51.52</v>
+      </c>
+      <c r="E11">
+        <v>51.52</v>
+      </c>
+      <c r="F11">
+        <v>45.45</v>
+      </c>
+      <c r="G11">
+        <v>48.48</v>
+      </c>
+      <c r="H11">
+        <v>42.42</v>
+      </c>
+      <c r="I11">
+        <v>45.45</v>
+      </c>
+      <c r="J11">
+        <v>45.45</v>
+      </c>
+      <c r="K11">
+        <v>45.45</v>
+      </c>
+      <c r="L11">
+        <v>48.48</v>
+      </c>
+      <c r="M11">
+        <v>48.48</v>
+      </c>
+      <c r="N11">
+        <v>48.48</v>
+      </c>
+      <c r="O11">
+        <v>48.48</v>
+      </c>
+      <c r="P11">
+        <v>48.48</v>
+      </c>
+      <c r="Q11">
+        <v>47.88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>49</v>
+      </c>
+      <c r="C12">
+        <v>47.42</v>
+      </c>
+      <c r="D12">
+        <v>48.73</v>
+      </c>
+      <c r="E12">
+        <v>50.33</v>
+      </c>
+      <c r="F12">
+        <v>52.39</v>
+      </c>
+      <c r="G12">
+        <v>50.3</v>
+      </c>
+      <c r="H12">
+        <v>52.64</v>
+      </c>
+      <c r="I12">
+        <v>53.94</v>
+      </c>
+      <c r="J12">
+        <v>53.64</v>
+      </c>
+      <c r="K12">
+        <v>54.97</v>
+      </c>
+      <c r="L12">
+        <v>52.88</v>
+      </c>
+      <c r="M12">
+        <v>54.54</v>
+      </c>
+      <c r="N12">
+        <v>55.21</v>
+      </c>
+      <c r="O12">
+        <v>54.55</v>
+      </c>
+      <c r="P12">
+        <v>53.55</v>
+      </c>
+      <c r="Q12">
+        <v>52.27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2099,49 +2925,49 @@
         <v>43.33</v>
       </c>
       <c r="C2">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>43.33</v>
       </c>
       <c r="E2">
-        <v>56.67</v>
+        <v>46.67</v>
       </c>
       <c r="F2">
-        <v>43.33</v>
+        <v>56.67</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>60</v>
       </c>
       <c r="I2">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="J2">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L2">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="M2">
-        <v>66.67</v>
+        <v>53.33</v>
       </c>
       <c r="N2">
-        <v>66.67</v>
+        <v>53.33</v>
       </c>
       <c r="O2">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="P2">
-        <v>56.67</v>
+        <v>60</v>
       </c>
       <c r="Q2">
-        <v>55.78</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -2152,49 +2978,49 @@
         <v>46.67</v>
       </c>
       <c r="C3">
-        <v>56.67</v>
+        <v>46.67</v>
       </c>
       <c r="D3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E3">
-        <v>43.33</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>46.67</v>
       </c>
       <c r="G3">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>63.33</v>
+        <v>50</v>
       </c>
       <c r="J3">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="K3">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="L3">
-        <v>53.33</v>
+        <v>46.67</v>
       </c>
       <c r="M3">
-        <v>50</v>
+        <v>43.33</v>
       </c>
       <c r="N3">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
       <c r="O3">
-        <v>56.67</v>
+        <v>46.67</v>
       </c>
       <c r="P3">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
       <c r="Q3">
-        <v>54.22</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -2202,52 +3028,52 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>46.67</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>43.33</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>46.67</v>
+        <v>43.33</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>36.67</v>
       </c>
       <c r="H4">
-        <v>56.67</v>
+        <v>36.67</v>
       </c>
       <c r="I4">
-        <v>53.33</v>
+        <v>43.33</v>
       </c>
       <c r="J4">
-        <v>50</v>
+        <v>43.33</v>
       </c>
       <c r="K4">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="L4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M4">
-        <v>46.67</v>
+        <v>43.33</v>
       </c>
       <c r="N4">
-        <v>43.33</v>
+        <v>46.67</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="P4">
         <v>50</v>
       </c>
       <c r="Q4">
-        <v>46.67</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -2258,19 +3084,19 @@
         <v>50</v>
       </c>
       <c r="C5">
-        <v>56.67</v>
+        <v>63.33</v>
       </c>
       <c r="D5">
-        <v>46.67</v>
+        <v>63.33</v>
       </c>
       <c r="E5">
         <v>60</v>
       </c>
       <c r="F5">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="G5">
-        <v>63.33</v>
+        <v>60</v>
       </c>
       <c r="H5">
         <v>60</v>
@@ -2279,28 +3105,28 @@
         <v>60</v>
       </c>
       <c r="J5">
-        <v>63.33</v>
+        <v>56.67</v>
       </c>
       <c r="K5">
-        <v>63.33</v>
+        <v>53.33</v>
       </c>
       <c r="L5">
         <v>56.67</v>
       </c>
       <c r="M5">
-        <v>63.33</v>
+        <v>60</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>63.33</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>66.67</v>
+        <v>53.33</v>
       </c>
       <c r="Q5">
-        <v>59.56</v>
+        <v>58.22</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -2308,52 +3134,52 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>33.33</v>
+        <v>43.33</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>43.33</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>43.33</v>
       </c>
       <c r="F6">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>26.67</v>
+        <v>46.67</v>
       </c>
       <c r="J6">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>36.67</v>
+        <v>46.67</v>
       </c>
       <c r="L6">
-        <v>33.33</v>
+        <v>46.67</v>
       </c>
       <c r="M6">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="N6">
-        <v>33.33</v>
+        <v>46.67</v>
       </c>
       <c r="O6">
-        <v>36.67</v>
+        <v>40</v>
       </c>
       <c r="P6">
-        <v>36.67</v>
+        <v>43.33</v>
       </c>
       <c r="Q6">
-        <v>34.89</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -2361,52 +3187,52 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>46.67</v>
+        <v>43.33</v>
       </c>
       <c r="C7">
-        <v>46.67</v>
+        <v>43.33</v>
       </c>
       <c r="D7">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>56.67</v>
       </c>
       <c r="F7">
-        <v>36.67</v>
+        <v>43.33</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>63.33</v>
       </c>
       <c r="H7">
-        <v>43.33</v>
+        <v>60</v>
       </c>
       <c r="I7">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="J7">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="K7">
         <v>66.67</v>
       </c>
       <c r="L7">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="N7">
         <v>56.67</v>
       </c>
       <c r="O7">
-        <v>56.67</v>
+        <v>60</v>
       </c>
       <c r="P7">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="Q7">
-        <v>54.22</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2414,52 +3240,52 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>46.67</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>36.67</v>
+        <v>53.33</v>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="J8">
-        <v>36.67</v>
+        <v>60</v>
       </c>
       <c r="K8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L8">
-        <v>36.67</v>
+        <v>46.67</v>
       </c>
       <c r="M8">
-        <v>33.33</v>
+        <v>43.33</v>
       </c>
       <c r="N8">
-        <v>43.33</v>
+        <v>46.67</v>
       </c>
       <c r="O8">
-        <v>43.33</v>
+        <v>50</v>
       </c>
       <c r="P8">
-        <v>36.67</v>
+        <v>50</v>
       </c>
       <c r="Q8">
-        <v>38.44</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -2467,43 +3293,43 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="C9">
-        <v>36.67</v>
+        <v>46.67</v>
       </c>
       <c r="D9">
         <v>50</v>
       </c>
       <c r="E9">
-        <v>56.67</v>
+        <v>46.67</v>
       </c>
       <c r="F9">
         <v>46.67</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>56.67</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>56.67</v>
       </c>
       <c r="J9">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="K9">
-        <v>46.67</v>
+        <v>56.67</v>
       </c>
       <c r="L9">
-        <v>43.33</v>
+        <v>50</v>
       </c>
       <c r="M9">
-        <v>43.33</v>
+        <v>53.33</v>
       </c>
       <c r="N9">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="O9">
         <v>50</v>
@@ -2512,7 +3338,7 @@
         <v>50</v>
       </c>
       <c r="Q9">
-        <v>48</v>
+        <v>51.78</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -2520,52 +3346,52 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>45.45</v>
+        <v>48.48</v>
       </c>
       <c r="C10">
+        <v>42.42</v>
+      </c>
+      <c r="D10">
+        <v>42.42</v>
+      </c>
+      <c r="E10">
+        <v>51.52</v>
+      </c>
+      <c r="F10">
+        <v>48.48</v>
+      </c>
+      <c r="G10">
+        <v>57.58</v>
+      </c>
+      <c r="H10">
+        <v>60.61</v>
+      </c>
+      <c r="I10">
+        <v>57.58</v>
+      </c>
+      <c r="J10">
         <v>54.55</v>
       </c>
-      <c r="D10">
+      <c r="K10">
         <v>54.55</v>
       </c>
-      <c r="E10">
+      <c r="L10">
         <v>63.64</v>
       </c>
-      <c r="F10">
-        <v>57.58</v>
-      </c>
-      <c r="G10">
-        <v>69.7</v>
-      </c>
-      <c r="H10">
-        <v>69.7</v>
-      </c>
-      <c r="I10">
+      <c r="M10">
         <v>66.67</v>
       </c>
-      <c r="J10">
-        <v>69.7</v>
-      </c>
-      <c r="K10">
-        <v>72.73</v>
-      </c>
-      <c r="L10">
-        <v>69.7</v>
-      </c>
-      <c r="M10">
-        <v>72.73</v>
-      </c>
       <c r="N10">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="O10">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="P10">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="Q10">
-        <v>65.66</v>
+        <v>56.57</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -2573,52 +3399,52 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>42.42</v>
+        <v>45.45</v>
       </c>
       <c r="C11">
+        <v>48.48</v>
+      </c>
+      <c r="D11">
         <v>51.52</v>
       </c>
-      <c r="D11">
-        <v>57.58</v>
-      </c>
       <c r="E11">
-        <v>60.61</v>
+        <v>48.48</v>
       </c>
       <c r="F11">
-        <v>51.52</v>
+        <v>48.48</v>
       </c>
       <c r="G11">
-        <v>48.48</v>
+        <v>45.45</v>
       </c>
       <c r="H11">
         <v>48.48</v>
       </c>
       <c r="I11">
+        <v>48.48</v>
+      </c>
+      <c r="J11">
         <v>42.42</v>
       </c>
-      <c r="J11">
+      <c r="K11">
+        <v>42.42</v>
+      </c>
+      <c r="L11">
+        <v>42.42</v>
+      </c>
+      <c r="M11">
+        <v>42.42</v>
+      </c>
+      <c r="N11">
         <v>45.45</v>
-      </c>
-      <c r="K11">
-        <v>51.52</v>
-      </c>
-      <c r="L11">
-        <v>54.55</v>
-      </c>
-      <c r="M11">
-        <v>51.52</v>
-      </c>
-      <c r="N11">
-        <v>48.48</v>
       </c>
       <c r="O11">
         <v>48.48</v>
       </c>
       <c r="P11">
-        <v>54.55</v>
+        <v>45.45</v>
       </c>
       <c r="Q11">
-        <v>50.51</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -2626,52 +3452,52 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>45.12</v>
+        <v>48.39</v>
       </c>
       <c r="C12">
-        <v>44.28</v>
+        <v>48.09</v>
       </c>
       <c r="D12">
-        <v>48.55</v>
+        <v>49.73</v>
       </c>
       <c r="E12">
-        <v>48.42</v>
+        <v>48</v>
       </c>
       <c r="F12">
-        <v>48.58</v>
+        <v>50.03</v>
       </c>
       <c r="G12">
-        <v>50.82</v>
+        <v>52.64</v>
       </c>
       <c r="H12">
-        <v>51.48</v>
+        <v>53.58</v>
       </c>
       <c r="I12">
-        <v>52.24</v>
+        <v>53.61</v>
       </c>
       <c r="J12">
-        <v>53.18</v>
+        <v>51.7</v>
       </c>
       <c r="K12">
-        <v>54.43</v>
+        <v>51.7</v>
       </c>
       <c r="L12">
-        <v>51.42</v>
+        <v>50.27</v>
       </c>
       <c r="M12">
-        <v>52.09</v>
+        <v>50.91</v>
       </c>
       <c r="N12">
-        <v>53.12</v>
+        <v>51.88</v>
       </c>
       <c r="O12">
-        <v>53.46</v>
+        <v>52.85</v>
       </c>
       <c r="P12">
-        <v>54.73</v>
+        <v>52.21</v>
       </c>
       <c r="Q12">
-        <v>50.79</v>
+        <v>51.04</v>
       </c>
     </row>
   </sheetData>
@@ -2679,12 +3505,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:Q12"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2716,25 +3542,10 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -2742,69 +3553,54 @@
         <v>43.33</v>
       </c>
       <c r="C2">
-        <v>53.33</v>
+        <v>56.67</v>
       </c>
       <c r="D2">
-        <v>63.33</v>
+        <v>56.67</v>
       </c>
       <c r="E2">
-        <v>66.67</v>
+        <v>43.33</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="G2">
-        <v>56.67</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="I2">
-        <v>56.67</v>
+        <v>53.33</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L2">
-        <v>66.67</v>
-      </c>
-      <c r="M2">
-        <v>63.33</v>
-      </c>
-      <c r="N2">
-        <v>56.67</v>
-      </c>
-      <c r="O2">
-        <v>56.67</v>
-      </c>
-      <c r="P2">
-        <v>60</v>
-      </c>
-      <c r="Q2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>50.33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>43.33</v>
+        <v>56.67</v>
       </c>
       <c r="C3">
-        <v>66.67</v>
+        <v>56.67</v>
       </c>
       <c r="D3">
-        <v>63.33</v>
+        <v>50</v>
       </c>
       <c r="E3">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>56.67</v>
       </c>
       <c r="G3">
         <v>53.33</v>
@@ -2816,84 +3612,54 @@
         <v>63.33</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>63.33</v>
       </c>
       <c r="K3">
-        <v>60</v>
+        <v>63.33</v>
       </c>
       <c r="L3">
-        <v>63.33</v>
-      </c>
-      <c r="M3">
-        <v>63.33</v>
-      </c>
-      <c r="N3">
-        <v>63.33</v>
-      </c>
-      <c r="O3">
-        <v>63.33</v>
-      </c>
-      <c r="P3">
-        <v>63.33</v>
-      </c>
-      <c r="Q3">
-        <v>59.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+        <v>56.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B4">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
         <v>33.33</v>
-      </c>
-      <c r="E4">
-        <v>36.67</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>56.67</v>
       </c>
       <c r="H4">
-        <v>36.67</v>
+        <v>46.67</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K4">
-        <v>40</v>
+        <v>46.67</v>
       </c>
       <c r="L4">
-        <v>46.67</v>
-      </c>
-      <c r="M4">
-        <v>46.67</v>
-      </c>
-      <c r="N4">
-        <v>46.67</v>
-      </c>
-      <c r="O4">
-        <v>53.33</v>
-      </c>
-      <c r="P4">
-        <v>53.33</v>
-      </c>
-      <c r="Q4">
-        <v>41.56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+        <v>45.67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -2901,10 +3667,10 @@
         <v>53.33</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="D5">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>66.67</v>
@@ -2913,408 +3679,288 @@
         <v>63.33</v>
       </c>
       <c r="G5">
-        <v>56.67</v>
+        <v>63.33</v>
       </c>
       <c r="H5">
         <v>56.67</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>63.33</v>
       </c>
       <c r="J5">
         <v>63.33</v>
       </c>
       <c r="K5">
-        <v>56.67</v>
+        <v>60</v>
       </c>
       <c r="L5">
-        <v>56.67</v>
-      </c>
-      <c r="M5">
-        <v>56.67</v>
-      </c>
-      <c r="N5">
-        <v>56.67</v>
-      </c>
-      <c r="O5">
-        <v>60</v>
-      </c>
-      <c r="P5">
-        <v>60</v>
-      </c>
-      <c r="Q5">
-        <v>58.67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>59.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="C6">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="D6">
+        <v>36.67</v>
+      </c>
+      <c r="E6">
+        <v>36.67</v>
+      </c>
+      <c r="F6">
         <v>30</v>
       </c>
-      <c r="E6">
-        <v>33.33</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
       <c r="G6">
-        <v>46.67</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I6">
         <v>33.33</v>
       </c>
       <c r="J6">
-        <v>26.67</v>
+        <v>33.33</v>
       </c>
       <c r="K6">
-        <v>36.67</v>
+        <v>30</v>
       </c>
       <c r="L6">
-        <v>36.67</v>
-      </c>
-      <c r="M6">
-        <v>33.33</v>
-      </c>
-      <c r="N6">
-        <v>30</v>
-      </c>
-      <c r="O6">
-        <v>30</v>
-      </c>
-      <c r="P6">
-        <v>33.33</v>
-      </c>
-      <c r="Q6">
-        <v>37.11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>35.67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B7">
-        <v>53.33</v>
+        <v>36.67</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>43.33</v>
       </c>
       <c r="D7">
+        <v>46.67</v>
+      </c>
+      <c r="E7">
+        <v>53.33</v>
+      </c>
+      <c r="F7">
+        <v>56.67</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7">
+        <v>56.67</v>
+      </c>
+      <c r="I7">
+        <v>63.33</v>
+      </c>
+      <c r="J7">
         <v>66.67</v>
-      </c>
-      <c r="E7">
-        <v>50</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>53.33</v>
-      </c>
-      <c r="H7">
-        <v>66.67</v>
-      </c>
-      <c r="I7">
-        <v>60</v>
-      </c>
-      <c r="J7">
-        <v>60</v>
       </c>
       <c r="K7">
         <v>66.67</v>
       </c>
       <c r="L7">
-        <v>63.33</v>
-      </c>
-      <c r="M7">
-        <v>63.33</v>
-      </c>
-      <c r="N7">
-        <v>63.33</v>
-      </c>
-      <c r="O7">
-        <v>63.33</v>
-      </c>
-      <c r="P7">
-        <v>66.67</v>
-      </c>
-      <c r="Q7">
-        <v>59.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>46.67</v>
+        <v>53.33</v>
       </c>
       <c r="C8">
+        <v>43.33</v>
+      </c>
+      <c r="D8">
+        <v>33.33</v>
+      </c>
+      <c r="E8">
+        <v>36.67</v>
+      </c>
+      <c r="F8">
+        <v>33.33</v>
+      </c>
+      <c r="G8">
         <v>26.67</v>
       </c>
-      <c r="D8">
-        <v>23.33</v>
-      </c>
-      <c r="E8">
+      <c r="H8">
+        <v>33.33</v>
+      </c>
+      <c r="I8">
         <v>30</v>
       </c>
-      <c r="F8">
-        <v>46.67</v>
-      </c>
-      <c r="G8">
-        <v>40</v>
-      </c>
-      <c r="H8">
-        <v>36.67</v>
-      </c>
-      <c r="I8">
+      <c r="J8">
+        <v>26.67</v>
+      </c>
+      <c r="K8">
         <v>33.33</v>
       </c>
-      <c r="J8">
-        <v>40</v>
-      </c>
-      <c r="K8">
-        <v>40</v>
-      </c>
       <c r="L8">
-        <v>43.33</v>
-      </c>
-      <c r="M8">
-        <v>43.33</v>
-      </c>
-      <c r="N8">
-        <v>43.33</v>
-      </c>
-      <c r="O8">
-        <v>40</v>
-      </c>
-      <c r="P8">
-        <v>40</v>
-      </c>
-      <c r="Q8">
-        <v>38.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>26.67</v>
+      </c>
+      <c r="D9">
+        <v>23.33</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
         <v>33.33</v>
       </c>
-      <c r="C9">
-        <v>43.33</v>
-      </c>
-      <c r="D9">
-        <v>46.67</v>
-      </c>
-      <c r="E9">
-        <v>43.33</v>
-      </c>
-      <c r="F9">
-        <v>50</v>
-      </c>
       <c r="G9">
-        <v>50</v>
+        <v>36.67</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>43.33</v>
       </c>
       <c r="I9">
-        <v>46.67</v>
+        <v>43.33</v>
       </c>
       <c r="J9">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="K9">
         <v>50</v>
       </c>
       <c r="L9">
-        <v>53.33</v>
-      </c>
-      <c r="M9">
-        <v>46.67</v>
-      </c>
-      <c r="N9">
-        <v>46.67</v>
-      </c>
-      <c r="O9">
-        <v>50</v>
-      </c>
-      <c r="P9">
-        <v>50</v>
-      </c>
-      <c r="Q9">
-        <v>47.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>37.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B10">
+        <v>48.48</v>
+      </c>
+      <c r="C10">
         <v>45.45</v>
       </c>
-      <c r="C10">
-        <v>51.52</v>
-      </c>
       <c r="D10">
+        <v>36.36</v>
+      </c>
+      <c r="E10">
         <v>60.61</v>
       </c>
-      <c r="E10">
-        <v>57.58</v>
-      </c>
       <c r="F10">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="G10">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H10">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="I10">
         <v>69.7</v>
       </c>
       <c r="J10">
-        <v>69.7</v>
+        <v>66.67</v>
       </c>
       <c r="K10">
-        <v>72.73</v>
+        <v>63.64</v>
       </c>
       <c r="L10">
-        <v>69.7</v>
-      </c>
-      <c r="M10">
-        <v>69.7</v>
-      </c>
-      <c r="N10">
-        <v>72.73</v>
-      </c>
-      <c r="O10">
-        <v>69.7</v>
-      </c>
-      <c r="P10">
-        <v>72.73</v>
-      </c>
-      <c r="Q10">
-        <v>65.66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B11">
-        <v>48.48</v>
+        <v>54.55</v>
       </c>
       <c r="C11">
-        <v>48.48</v>
+        <v>45.45</v>
       </c>
       <c r="D11">
-        <v>42.42</v>
+        <v>51.52</v>
       </c>
       <c r="E11">
-        <v>45.45</v>
+        <v>57.58</v>
       </c>
       <c r="F11">
-        <v>48.48</v>
+        <v>57.58</v>
       </c>
       <c r="G11">
-        <v>48.48</v>
+        <v>57.58</v>
       </c>
       <c r="H11">
-        <v>42.42</v>
+        <v>57.58</v>
       </c>
       <c r="I11">
-        <v>36.36</v>
+        <v>54.55</v>
       </c>
       <c r="J11">
-        <v>39.39</v>
+        <v>51.52</v>
       </c>
       <c r="K11">
-        <v>45.45</v>
+        <v>57.58</v>
       </c>
       <c r="L11">
-        <v>48.48</v>
-      </c>
-      <c r="M11">
-        <v>51.52</v>
-      </c>
-      <c r="N11">
         <v>54.55</v>
       </c>
-      <c r="O11">
-        <v>48.48</v>
-      </c>
-      <c r="P11">
-        <v>48.48</v>
-      </c>
-      <c r="Q11">
-        <v>46.46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>45.72</v>
+        <v>46.64</v>
       </c>
       <c r="C12">
-        <v>47.67</v>
+        <v>47.09</v>
       </c>
       <c r="D12">
-        <v>48.3</v>
+        <v>44.46</v>
       </c>
       <c r="E12">
-        <v>48.64</v>
+        <v>46.15</v>
       </c>
       <c r="F12">
-        <v>50.21</v>
+        <v>47.42</v>
       </c>
       <c r="G12">
-        <v>51.48</v>
+        <v>50.7</v>
       </c>
       <c r="H12">
-        <v>51.21</v>
+        <v>50.7</v>
       </c>
       <c r="I12">
-        <v>49.94</v>
+        <v>52.42</v>
       </c>
       <c r="J12">
-        <v>50.91</v>
+        <v>51.82</v>
       </c>
       <c r="K12">
-        <v>52.82</v>
+        <v>52.12</v>
       </c>
       <c r="L12">
-        <v>54.82</v>
-      </c>
-      <c r="M12">
-        <v>53.79</v>
-      </c>
-      <c r="N12">
-        <v>53.4</v>
-      </c>
-      <c r="O12">
-        <v>53.48</v>
-      </c>
-      <c r="P12">
-        <v>54.79</v>
-      </c>
-      <c r="Q12">
-        <v>51.15</v>
+        <v>48.95</v>
       </c>
     </row>
   </sheetData>
@@ -3322,650 +3968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
-        <v>40</v>
-      </c>
-      <c r="C2">
-        <v>46.67</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>60</v>
-      </c>
-      <c r="F2">
-        <v>56.67</v>
-      </c>
-      <c r="G2">
-        <v>60</v>
-      </c>
-      <c r="H2">
-        <v>56.67</v>
-      </c>
-      <c r="I2">
-        <v>70</v>
-      </c>
-      <c r="J2">
-        <v>73.33</v>
-      </c>
-      <c r="K2">
-        <v>70</v>
-      </c>
-      <c r="L2">
-        <v>66.67</v>
-      </c>
-      <c r="M2">
-        <v>63.33</v>
-      </c>
-      <c r="N2">
-        <v>63.33</v>
-      </c>
-      <c r="O2">
-        <v>70</v>
-      </c>
-      <c r="P2">
-        <v>70</v>
-      </c>
-      <c r="Q2">
-        <v>61.11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>53.33</v>
-      </c>
-      <c r="C3">
-        <v>46.67</v>
-      </c>
-      <c r="D3">
-        <v>60</v>
-      </c>
-      <c r="E3">
-        <v>50</v>
-      </c>
-      <c r="F3">
-        <v>46.67</v>
-      </c>
-      <c r="G3">
-        <v>46.67</v>
-      </c>
-      <c r="H3">
-        <v>53.33</v>
-      </c>
-      <c r="I3">
-        <v>46.67</v>
-      </c>
-      <c r="J3">
-        <v>46.67</v>
-      </c>
-      <c r="K3">
-        <v>50</v>
-      </c>
-      <c r="L3">
-        <v>53.33</v>
-      </c>
-      <c r="M3">
-        <v>50</v>
-      </c>
-      <c r="N3">
-        <v>53.33</v>
-      </c>
-      <c r="O3">
-        <v>56.67</v>
-      </c>
-      <c r="P3">
-        <v>53.33</v>
-      </c>
-      <c r="Q3">
-        <v>51.11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
-        <v>33.33</v>
-      </c>
-      <c r="C4">
-        <v>46.67</v>
-      </c>
-      <c r="D4">
-        <v>36.67</v>
-      </c>
-      <c r="E4">
-        <v>36.67</v>
-      </c>
-      <c r="F4">
-        <v>53.33</v>
-      </c>
-      <c r="G4">
-        <v>40</v>
-      </c>
-      <c r="H4">
-        <v>36.67</v>
-      </c>
-      <c r="I4">
-        <v>40</v>
-      </c>
-      <c r="J4">
-        <v>40</v>
-      </c>
-      <c r="K4">
-        <v>43.33</v>
-      </c>
-      <c r="L4">
-        <v>40</v>
-      </c>
-      <c r="M4">
-        <v>50</v>
-      </c>
-      <c r="N4">
-        <v>46.67</v>
-      </c>
-      <c r="O4">
-        <v>46.67</v>
-      </c>
-      <c r="P4">
-        <v>43.33</v>
-      </c>
-      <c r="Q4">
-        <v>42.22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>50</v>
-      </c>
-      <c r="C5">
-        <v>56.67</v>
-      </c>
-      <c r="D5">
-        <v>53.33</v>
-      </c>
-      <c r="E5">
-        <v>53.33</v>
-      </c>
-      <c r="F5">
-        <v>50</v>
-      </c>
-      <c r="G5">
-        <v>50</v>
-      </c>
-      <c r="H5">
-        <v>53.33</v>
-      </c>
-      <c r="I5">
-        <v>50</v>
-      </c>
-      <c r="J5">
-        <v>53.33</v>
-      </c>
-      <c r="K5">
-        <v>56.67</v>
-      </c>
-      <c r="L5">
-        <v>56.67</v>
-      </c>
-      <c r="M5">
-        <v>50</v>
-      </c>
-      <c r="N5">
-        <v>53.33</v>
-      </c>
-      <c r="O5">
-        <v>56.67</v>
-      </c>
-      <c r="P5">
-        <v>56.67</v>
-      </c>
-      <c r="Q5">
-        <v>53.33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>46.67</v>
-      </c>
-      <c r="C6">
-        <v>43.33</v>
-      </c>
-      <c r="D6">
-        <v>23.33</v>
-      </c>
-      <c r="E6">
-        <v>33.33</v>
-      </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>36.67</v>
-      </c>
-      <c r="H6">
-        <v>36.67</v>
-      </c>
-      <c r="I6">
-        <v>36.67</v>
-      </c>
-      <c r="J6">
-        <v>33.33</v>
-      </c>
-      <c r="K6">
-        <v>36.67</v>
-      </c>
-      <c r="L6">
-        <v>33.33</v>
-      </c>
-      <c r="M6">
-        <v>30</v>
-      </c>
-      <c r="N6">
-        <v>30</v>
-      </c>
-      <c r="O6">
-        <v>33.33</v>
-      </c>
-      <c r="P6">
-        <v>36.67</v>
-      </c>
-      <c r="Q6">
-        <v>34.67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>53.33</v>
-      </c>
-      <c r="C7">
-        <v>43.33</v>
-      </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7">
-        <v>50</v>
-      </c>
-      <c r="F7">
-        <v>63.33</v>
-      </c>
-      <c r="G7">
-        <v>60</v>
-      </c>
-      <c r="H7">
-        <v>50</v>
-      </c>
-      <c r="I7">
-        <v>60</v>
-      </c>
-      <c r="J7">
-        <v>63.33</v>
-      </c>
-      <c r="K7">
-        <v>73.33</v>
-      </c>
-      <c r="L7">
-        <v>70</v>
-      </c>
-      <c r="M7">
-        <v>66.67</v>
-      </c>
-      <c r="N7">
-        <v>66.67</v>
-      </c>
-      <c r="O7">
-        <v>73.33</v>
-      </c>
-      <c r="P7">
-        <v>70</v>
-      </c>
-      <c r="Q7">
-        <v>60.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>50</v>
-      </c>
-      <c r="C8">
-        <v>30</v>
-      </c>
-      <c r="D8">
-        <v>46.67</v>
-      </c>
-      <c r="E8">
-        <v>56.67</v>
-      </c>
-      <c r="F8">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>60</v>
-      </c>
-      <c r="H8">
-        <v>63.33</v>
-      </c>
-      <c r="I8">
-        <v>56.67</v>
-      </c>
-      <c r="J8">
-        <v>63.33</v>
-      </c>
-      <c r="K8">
-        <v>66.67</v>
-      </c>
-      <c r="L8">
-        <v>63.33</v>
-      </c>
-      <c r="M8">
-        <v>56.67</v>
-      </c>
-      <c r="N8">
-        <v>56.67</v>
-      </c>
-      <c r="O8">
-        <v>53.33</v>
-      </c>
-      <c r="P8">
-        <v>53.33</v>
-      </c>
-      <c r="Q8">
-        <v>55.78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
-        <v>46.67</v>
-      </c>
-      <c r="C9">
-        <v>36.67</v>
-      </c>
-      <c r="D9">
-        <v>50</v>
-      </c>
-      <c r="E9">
-        <v>50</v>
-      </c>
-      <c r="F9">
-        <v>53.33</v>
-      </c>
-      <c r="G9">
-        <v>56.67</v>
-      </c>
-      <c r="H9">
-        <v>53.33</v>
-      </c>
-      <c r="I9">
-        <v>53.33</v>
-      </c>
-      <c r="J9">
-        <v>56.67</v>
-      </c>
-      <c r="K9">
-        <v>56.67</v>
-      </c>
-      <c r="L9">
-        <v>53.33</v>
-      </c>
-      <c r="M9">
-        <v>53.33</v>
-      </c>
-      <c r="N9">
-        <v>50</v>
-      </c>
-      <c r="O9">
-        <v>53.33</v>
-      </c>
-      <c r="P9">
-        <v>56.67</v>
-      </c>
-      <c r="Q9">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>48.48</v>
-      </c>
-      <c r="C10">
-        <v>45.45</v>
-      </c>
-      <c r="D10">
-        <v>51.52</v>
-      </c>
-      <c r="E10">
-        <v>54.55</v>
-      </c>
-      <c r="F10">
-        <v>54.55</v>
-      </c>
-      <c r="G10">
-        <v>60.61</v>
-      </c>
-      <c r="H10">
-        <v>66.67</v>
-      </c>
-      <c r="I10">
-        <v>66.67</v>
-      </c>
-      <c r="J10">
-        <v>66.67</v>
-      </c>
-      <c r="K10">
-        <v>66.67</v>
-      </c>
-      <c r="L10">
-        <v>63.64</v>
-      </c>
-      <c r="M10">
-        <v>63.64</v>
-      </c>
-      <c r="N10">
-        <v>60.61</v>
-      </c>
-      <c r="O10">
-        <v>60.61</v>
-      </c>
-      <c r="P10">
-        <v>66.67</v>
-      </c>
-      <c r="Q10">
-        <v>59.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
-        <v>45.45</v>
-      </c>
-      <c r="C11">
-        <v>45.45</v>
-      </c>
-      <c r="D11">
-        <v>51.52</v>
-      </c>
-      <c r="E11">
-        <v>54.55</v>
-      </c>
-      <c r="F11">
-        <v>45.45</v>
-      </c>
-      <c r="G11">
-        <v>54.55</v>
-      </c>
-      <c r="H11">
-        <v>51.52</v>
-      </c>
-      <c r="I11">
-        <v>42.42</v>
-      </c>
-      <c r="J11">
-        <v>48.48</v>
-      </c>
-      <c r="K11">
-        <v>48.48</v>
-      </c>
-      <c r="L11">
-        <v>51.52</v>
-      </c>
-      <c r="M11">
-        <v>48.48</v>
-      </c>
-      <c r="N11">
-        <v>51.52</v>
-      </c>
-      <c r="O11">
-        <v>51.52</v>
-      </c>
-      <c r="P11">
-        <v>51.52</v>
-      </c>
-      <c r="Q11">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>46.73</v>
-      </c>
-      <c r="C12">
-        <v>44.09</v>
-      </c>
-      <c r="D12">
-        <v>46.3</v>
-      </c>
-      <c r="E12">
-        <v>49.91</v>
-      </c>
-      <c r="F12">
-        <v>51.33</v>
-      </c>
-      <c r="G12">
-        <v>52.52</v>
-      </c>
-      <c r="H12">
-        <v>52.15</v>
-      </c>
-      <c r="I12">
-        <v>52.24</v>
-      </c>
-      <c r="J12">
-        <v>54.51</v>
-      </c>
-      <c r="K12">
-        <v>56.85</v>
-      </c>
-      <c r="L12">
-        <v>55.18</v>
-      </c>
-      <c r="M12">
-        <v>53.21</v>
-      </c>
-      <c r="N12">
-        <v>53.21</v>
-      </c>
-      <c r="O12">
-        <v>55.55</v>
-      </c>
-      <c r="P12">
-        <v>55.82</v>
-      </c>
-      <c r="Q12">
-        <v>51.97</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4025,6 +4028,1935 @@
         <v>16</v>
       </c>
       <c r="B2">
+        <v>43.33</v>
+      </c>
+      <c r="C2">
+        <v>46.67</v>
+      </c>
+      <c r="D2">
+        <v>60</v>
+      </c>
+      <c r="E2">
+        <v>56.67</v>
+      </c>
+      <c r="F2">
+        <v>43.33</v>
+      </c>
+      <c r="G2">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>60</v>
+      </c>
+      <c r="I2">
+        <v>56.67</v>
+      </c>
+      <c r="J2">
+        <v>56.67</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>56.67</v>
+      </c>
+      <c r="M2">
+        <v>66.67</v>
+      </c>
+      <c r="N2">
+        <v>66.67</v>
+      </c>
+      <c r="O2">
+        <v>56.67</v>
+      </c>
+      <c r="P2">
+        <v>56.67</v>
+      </c>
+      <c r="Q2">
+        <v>55.78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>46.67</v>
+      </c>
+      <c r="C3">
+        <v>56.67</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>43.33</v>
+      </c>
+      <c r="F3">
+        <v>46.67</v>
+      </c>
+      <c r="G3">
+        <v>53.33</v>
+      </c>
+      <c r="H3">
+        <v>56.67</v>
+      </c>
+      <c r="I3">
+        <v>63.33</v>
+      </c>
+      <c r="J3">
+        <v>56.67</v>
+      </c>
+      <c r="K3">
+        <v>56.67</v>
+      </c>
+      <c r="L3">
+        <v>53.33</v>
+      </c>
+      <c r="M3">
+        <v>50</v>
+      </c>
+      <c r="N3">
+        <v>56.67</v>
+      </c>
+      <c r="O3">
+        <v>56.67</v>
+      </c>
+      <c r="P3">
+        <v>56.67</v>
+      </c>
+      <c r="Q3">
+        <v>54.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>43.33</v>
+      </c>
+      <c r="F4">
+        <v>46.67</v>
+      </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>56.67</v>
+      </c>
+      <c r="I4">
+        <v>53.33</v>
+      </c>
+      <c r="J4">
+        <v>50</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>46.67</v>
+      </c>
+      <c r="N4">
+        <v>43.33</v>
+      </c>
+      <c r="O4">
+        <v>50</v>
+      </c>
+      <c r="P4">
+        <v>50</v>
+      </c>
+      <c r="Q4">
+        <v>46.67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>56.67</v>
+      </c>
+      <c r="D5">
+        <v>46.67</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>63.33</v>
+      </c>
+      <c r="H5">
+        <v>60</v>
+      </c>
+      <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5">
+        <v>63.33</v>
+      </c>
+      <c r="K5">
+        <v>63.33</v>
+      </c>
+      <c r="L5">
+        <v>56.67</v>
+      </c>
+      <c r="M5">
+        <v>63.33</v>
+      </c>
+      <c r="N5">
+        <v>60</v>
+      </c>
+      <c r="O5">
+        <v>63.33</v>
+      </c>
+      <c r="P5">
+        <v>66.67</v>
+      </c>
+      <c r="Q5">
+        <v>59.56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>46.67</v>
+      </c>
+      <c r="C6">
+        <v>33.33</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>46.67</v>
+      </c>
+      <c r="G6">
+        <v>33.33</v>
+      </c>
+      <c r="H6">
+        <v>33.33</v>
+      </c>
+      <c r="I6">
+        <v>26.67</v>
+      </c>
+      <c r="J6">
+        <v>33.33</v>
+      </c>
+      <c r="K6">
+        <v>36.67</v>
+      </c>
+      <c r="L6">
+        <v>33.33</v>
+      </c>
+      <c r="M6">
+        <v>33.33</v>
+      </c>
+      <c r="N6">
+        <v>33.33</v>
+      </c>
+      <c r="O6">
+        <v>36.67</v>
+      </c>
+      <c r="P6">
+        <v>36.67</v>
+      </c>
+      <c r="Q6">
+        <v>34.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>46.67</v>
+      </c>
+      <c r="C7">
+        <v>46.67</v>
+      </c>
+      <c r="D7">
+        <v>56.67</v>
+      </c>
+      <c r="E7">
+        <v>40</v>
+      </c>
+      <c r="F7">
+        <v>36.67</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>43.33</v>
+      </c>
+      <c r="I7">
+        <v>63.33</v>
+      </c>
+      <c r="J7">
+        <v>63.33</v>
+      </c>
+      <c r="K7">
+        <v>66.67</v>
+      </c>
+      <c r="L7">
+        <v>60</v>
+      </c>
+      <c r="M7">
+        <v>60</v>
+      </c>
+      <c r="N7">
+        <v>56.67</v>
+      </c>
+      <c r="O7">
+        <v>56.67</v>
+      </c>
+      <c r="P7">
+        <v>66.67</v>
+      </c>
+      <c r="Q7">
+        <v>54.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>36.67</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>36.67</v>
+      </c>
+      <c r="K8">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>36.67</v>
+      </c>
+      <c r="M8">
+        <v>33.33</v>
+      </c>
+      <c r="N8">
+        <v>43.33</v>
+      </c>
+      <c r="O8">
+        <v>43.33</v>
+      </c>
+      <c r="P8">
+        <v>36.67</v>
+      </c>
+      <c r="Q8">
+        <v>38.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>36.67</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>56.67</v>
+      </c>
+      <c r="F9">
+        <v>46.67</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>50</v>
+      </c>
+      <c r="I9">
+        <v>50</v>
+      </c>
+      <c r="J9">
+        <v>56.67</v>
+      </c>
+      <c r="K9">
+        <v>46.67</v>
+      </c>
+      <c r="L9">
+        <v>43.33</v>
+      </c>
+      <c r="M9">
+        <v>43.33</v>
+      </c>
+      <c r="N9">
+        <v>50</v>
+      </c>
+      <c r="O9">
+        <v>50</v>
+      </c>
+      <c r="P9">
+        <v>50</v>
+      </c>
+      <c r="Q9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>45.45</v>
+      </c>
+      <c r="C10">
+        <v>54.55</v>
+      </c>
+      <c r="D10">
+        <v>54.55</v>
+      </c>
+      <c r="E10">
+        <v>63.64</v>
+      </c>
+      <c r="F10">
+        <v>57.58</v>
+      </c>
+      <c r="G10">
+        <v>69.7</v>
+      </c>
+      <c r="H10">
+        <v>69.7</v>
+      </c>
+      <c r="I10">
+        <v>66.67</v>
+      </c>
+      <c r="J10">
+        <v>69.7</v>
+      </c>
+      <c r="K10">
+        <v>72.73</v>
+      </c>
+      <c r="L10">
+        <v>69.7</v>
+      </c>
+      <c r="M10">
+        <v>72.73</v>
+      </c>
+      <c r="N10">
+        <v>72.73</v>
+      </c>
+      <c r="O10">
+        <v>72.73</v>
+      </c>
+      <c r="P10">
+        <v>72.73</v>
+      </c>
+      <c r="Q10">
+        <v>65.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>42.42</v>
+      </c>
+      <c r="C11">
+        <v>51.52</v>
+      </c>
+      <c r="D11">
+        <v>57.58</v>
+      </c>
+      <c r="E11">
+        <v>60.61</v>
+      </c>
+      <c r="F11">
+        <v>51.52</v>
+      </c>
+      <c r="G11">
+        <v>48.48</v>
+      </c>
+      <c r="H11">
+        <v>48.48</v>
+      </c>
+      <c r="I11">
+        <v>42.42</v>
+      </c>
+      <c r="J11">
+        <v>45.45</v>
+      </c>
+      <c r="K11">
+        <v>51.52</v>
+      </c>
+      <c r="L11">
+        <v>54.55</v>
+      </c>
+      <c r="M11">
+        <v>51.52</v>
+      </c>
+      <c r="N11">
+        <v>48.48</v>
+      </c>
+      <c r="O11">
+        <v>48.48</v>
+      </c>
+      <c r="P11">
+        <v>54.55</v>
+      </c>
+      <c r="Q11">
+        <v>50.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>45.12</v>
+      </c>
+      <c r="C12">
+        <v>44.28</v>
+      </c>
+      <c r="D12">
+        <v>48.55</v>
+      </c>
+      <c r="E12">
+        <v>48.42</v>
+      </c>
+      <c r="F12">
+        <v>48.58</v>
+      </c>
+      <c r="G12">
+        <v>50.82</v>
+      </c>
+      <c r="H12">
+        <v>51.48</v>
+      </c>
+      <c r="I12">
+        <v>52.24</v>
+      </c>
+      <c r="J12">
+        <v>53.18</v>
+      </c>
+      <c r="K12">
+        <v>54.43</v>
+      </c>
+      <c r="L12">
+        <v>51.42</v>
+      </c>
+      <c r="M12">
+        <v>52.09</v>
+      </c>
+      <c r="N12">
+        <v>53.12</v>
+      </c>
+      <c r="O12">
+        <v>53.46</v>
+      </c>
+      <c r="P12">
+        <v>54.73</v>
+      </c>
+      <c r="Q12">
+        <v>50.79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>43.33</v>
+      </c>
+      <c r="C2">
+        <v>53.33</v>
+      </c>
+      <c r="D2">
+        <v>63.33</v>
+      </c>
+      <c r="E2">
+        <v>66.67</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>56.67</v>
+      </c>
+      <c r="H2">
+        <v>56.67</v>
+      </c>
+      <c r="I2">
+        <v>56.67</v>
+      </c>
+      <c r="J2">
+        <v>60</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>66.67</v>
+      </c>
+      <c r="M2">
+        <v>63.33</v>
+      </c>
+      <c r="N2">
+        <v>56.67</v>
+      </c>
+      <c r="O2">
+        <v>56.67</v>
+      </c>
+      <c r="P2">
+        <v>60</v>
+      </c>
+      <c r="Q2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>43.33</v>
+      </c>
+      <c r="C3">
+        <v>66.67</v>
+      </c>
+      <c r="D3">
+        <v>63.33</v>
+      </c>
+      <c r="E3">
+        <v>56.67</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>53.33</v>
+      </c>
+      <c r="H3">
+        <v>56.67</v>
+      </c>
+      <c r="I3">
+        <v>63.33</v>
+      </c>
+      <c r="J3">
+        <v>60</v>
+      </c>
+      <c r="K3">
+        <v>60</v>
+      </c>
+      <c r="L3">
+        <v>63.33</v>
+      </c>
+      <c r="M3">
+        <v>63.33</v>
+      </c>
+      <c r="N3">
+        <v>63.33</v>
+      </c>
+      <c r="O3">
+        <v>63.33</v>
+      </c>
+      <c r="P3">
+        <v>63.33</v>
+      </c>
+      <c r="Q3">
+        <v>59.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>33.33</v>
+      </c>
+      <c r="E4">
+        <v>36.67</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>36.67</v>
+      </c>
+      <c r="I4">
+        <v>40</v>
+      </c>
+      <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>40</v>
+      </c>
+      <c r="L4">
+        <v>46.67</v>
+      </c>
+      <c r="M4">
+        <v>46.67</v>
+      </c>
+      <c r="N4">
+        <v>46.67</v>
+      </c>
+      <c r="O4">
+        <v>53.33</v>
+      </c>
+      <c r="P4">
+        <v>53.33</v>
+      </c>
+      <c r="Q4">
+        <v>41.56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>53.33</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>53.33</v>
+      </c>
+      <c r="E5">
+        <v>66.67</v>
+      </c>
+      <c r="F5">
+        <v>63.33</v>
+      </c>
+      <c r="G5">
+        <v>56.67</v>
+      </c>
+      <c r="H5">
+        <v>56.67</v>
+      </c>
+      <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5">
+        <v>63.33</v>
+      </c>
+      <c r="K5">
+        <v>56.67</v>
+      </c>
+      <c r="L5">
+        <v>56.67</v>
+      </c>
+      <c r="M5">
+        <v>56.67</v>
+      </c>
+      <c r="N5">
+        <v>56.67</v>
+      </c>
+      <c r="O5">
+        <v>60</v>
+      </c>
+      <c r="P5">
+        <v>60</v>
+      </c>
+      <c r="Q5">
+        <v>58.67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>46.67</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>33.33</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>46.67</v>
+      </c>
+      <c r="H6">
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>33.33</v>
+      </c>
+      <c r="J6">
+        <v>26.67</v>
+      </c>
+      <c r="K6">
+        <v>36.67</v>
+      </c>
+      <c r="L6">
+        <v>36.67</v>
+      </c>
+      <c r="M6">
+        <v>33.33</v>
+      </c>
+      <c r="N6">
+        <v>30</v>
+      </c>
+      <c r="O6">
+        <v>30</v>
+      </c>
+      <c r="P6">
+        <v>33.33</v>
+      </c>
+      <c r="Q6">
+        <v>37.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>53.33</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>66.67</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>53.33</v>
+      </c>
+      <c r="H7">
+        <v>66.67</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>66.67</v>
+      </c>
+      <c r="L7">
+        <v>63.33</v>
+      </c>
+      <c r="M7">
+        <v>63.33</v>
+      </c>
+      <c r="N7">
+        <v>63.33</v>
+      </c>
+      <c r="O7">
+        <v>63.33</v>
+      </c>
+      <c r="P7">
+        <v>66.67</v>
+      </c>
+      <c r="Q7">
+        <v>59.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>46.67</v>
+      </c>
+      <c r="C8">
+        <v>26.67</v>
+      </c>
+      <c r="D8">
+        <v>23.33</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>46.67</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>36.67</v>
+      </c>
+      <c r="I8">
+        <v>33.33</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>43.33</v>
+      </c>
+      <c r="M8">
+        <v>43.33</v>
+      </c>
+      <c r="N8">
+        <v>43.33</v>
+      </c>
+      <c r="O8">
+        <v>40</v>
+      </c>
+      <c r="P8">
+        <v>40</v>
+      </c>
+      <c r="Q8">
+        <v>38.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>33.33</v>
+      </c>
+      <c r="C9">
+        <v>43.33</v>
+      </c>
+      <c r="D9">
+        <v>46.67</v>
+      </c>
+      <c r="E9">
+        <v>43.33</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>50</v>
+      </c>
+      <c r="I9">
+        <v>46.67</v>
+      </c>
+      <c r="J9">
+        <v>50</v>
+      </c>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9">
+        <v>53.33</v>
+      </c>
+      <c r="M9">
+        <v>46.67</v>
+      </c>
+      <c r="N9">
+        <v>46.67</v>
+      </c>
+      <c r="O9">
+        <v>50</v>
+      </c>
+      <c r="P9">
+        <v>50</v>
+      </c>
+      <c r="Q9">
+        <v>47.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>45.45</v>
+      </c>
+      <c r="C10">
+        <v>51.52</v>
+      </c>
+      <c r="D10">
+        <v>60.61</v>
+      </c>
+      <c r="E10">
+        <v>57.58</v>
+      </c>
+      <c r="F10">
+        <v>63.64</v>
+      </c>
+      <c r="G10">
+        <v>69.7</v>
+      </c>
+      <c r="H10">
+        <v>69.7</v>
+      </c>
+      <c r="I10">
+        <v>69.7</v>
+      </c>
+      <c r="J10">
+        <v>69.7</v>
+      </c>
+      <c r="K10">
+        <v>72.73</v>
+      </c>
+      <c r="L10">
+        <v>69.7</v>
+      </c>
+      <c r="M10">
+        <v>69.7</v>
+      </c>
+      <c r="N10">
+        <v>72.73</v>
+      </c>
+      <c r="O10">
+        <v>69.7</v>
+      </c>
+      <c r="P10">
+        <v>72.73</v>
+      </c>
+      <c r="Q10">
+        <v>65.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>48.48</v>
+      </c>
+      <c r="C11">
+        <v>48.48</v>
+      </c>
+      <c r="D11">
+        <v>42.42</v>
+      </c>
+      <c r="E11">
+        <v>45.45</v>
+      </c>
+      <c r="F11">
+        <v>48.48</v>
+      </c>
+      <c r="G11">
+        <v>48.48</v>
+      </c>
+      <c r="H11">
+        <v>42.42</v>
+      </c>
+      <c r="I11">
+        <v>36.36</v>
+      </c>
+      <c r="J11">
+        <v>39.39</v>
+      </c>
+      <c r="K11">
+        <v>45.45</v>
+      </c>
+      <c r="L11">
+        <v>48.48</v>
+      </c>
+      <c r="M11">
+        <v>51.52</v>
+      </c>
+      <c r="N11">
+        <v>54.55</v>
+      </c>
+      <c r="O11">
+        <v>48.48</v>
+      </c>
+      <c r="P11">
+        <v>48.48</v>
+      </c>
+      <c r="Q11">
+        <v>46.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>45.72</v>
+      </c>
+      <c r="C12">
+        <v>47.67</v>
+      </c>
+      <c r="D12">
+        <v>48.3</v>
+      </c>
+      <c r="E12">
+        <v>48.64</v>
+      </c>
+      <c r="F12">
+        <v>50.21</v>
+      </c>
+      <c r="G12">
+        <v>51.48</v>
+      </c>
+      <c r="H12">
+        <v>51.21</v>
+      </c>
+      <c r="I12">
+        <v>49.94</v>
+      </c>
+      <c r="J12">
+        <v>50.91</v>
+      </c>
+      <c r="K12">
+        <v>52.82</v>
+      </c>
+      <c r="L12">
+        <v>54.82</v>
+      </c>
+      <c r="M12">
+        <v>53.79</v>
+      </c>
+      <c r="N12">
+        <v>53.4</v>
+      </c>
+      <c r="O12">
+        <v>53.48</v>
+      </c>
+      <c r="P12">
+        <v>54.79</v>
+      </c>
+      <c r="Q12">
+        <v>51.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>40</v>
+      </c>
+      <c r="C2">
+        <v>46.67</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>60</v>
+      </c>
+      <c r="F2">
+        <v>56.67</v>
+      </c>
+      <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>56.67</v>
+      </c>
+      <c r="I2">
+        <v>70</v>
+      </c>
+      <c r="J2">
+        <v>73.33</v>
+      </c>
+      <c r="K2">
+        <v>70</v>
+      </c>
+      <c r="L2">
+        <v>66.67</v>
+      </c>
+      <c r="M2">
+        <v>63.33</v>
+      </c>
+      <c r="N2">
+        <v>63.33</v>
+      </c>
+      <c r="O2">
+        <v>70</v>
+      </c>
+      <c r="P2">
+        <v>70</v>
+      </c>
+      <c r="Q2">
+        <v>61.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>53.33</v>
+      </c>
+      <c r="C3">
+        <v>46.67</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>46.67</v>
+      </c>
+      <c r="G3">
+        <v>46.67</v>
+      </c>
+      <c r="H3">
+        <v>53.33</v>
+      </c>
+      <c r="I3">
+        <v>46.67</v>
+      </c>
+      <c r="J3">
+        <v>46.67</v>
+      </c>
+      <c r="K3">
+        <v>50</v>
+      </c>
+      <c r="L3">
+        <v>53.33</v>
+      </c>
+      <c r="M3">
+        <v>50</v>
+      </c>
+      <c r="N3">
+        <v>53.33</v>
+      </c>
+      <c r="O3">
+        <v>56.67</v>
+      </c>
+      <c r="P3">
+        <v>53.33</v>
+      </c>
+      <c r="Q3">
+        <v>51.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>33.33</v>
+      </c>
+      <c r="C4">
+        <v>46.67</v>
+      </c>
+      <c r="D4">
+        <v>36.67</v>
+      </c>
+      <c r="E4">
+        <v>36.67</v>
+      </c>
+      <c r="F4">
+        <v>53.33</v>
+      </c>
+      <c r="G4">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>36.67</v>
+      </c>
+      <c r="I4">
+        <v>40</v>
+      </c>
+      <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>43.33</v>
+      </c>
+      <c r="L4">
+        <v>40</v>
+      </c>
+      <c r="M4">
+        <v>50</v>
+      </c>
+      <c r="N4">
+        <v>46.67</v>
+      </c>
+      <c r="O4">
+        <v>46.67</v>
+      </c>
+      <c r="P4">
+        <v>43.33</v>
+      </c>
+      <c r="Q4">
+        <v>42.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>56.67</v>
+      </c>
+      <c r="D5">
+        <v>53.33</v>
+      </c>
+      <c r="E5">
+        <v>53.33</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>53.33</v>
+      </c>
+      <c r="I5">
+        <v>50</v>
+      </c>
+      <c r="J5">
+        <v>53.33</v>
+      </c>
+      <c r="K5">
+        <v>56.67</v>
+      </c>
+      <c r="L5">
+        <v>56.67</v>
+      </c>
+      <c r="M5">
+        <v>50</v>
+      </c>
+      <c r="N5">
+        <v>53.33</v>
+      </c>
+      <c r="O5">
+        <v>56.67</v>
+      </c>
+      <c r="P5">
+        <v>56.67</v>
+      </c>
+      <c r="Q5">
+        <v>53.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>46.67</v>
+      </c>
+      <c r="C6">
+        <v>43.33</v>
+      </c>
+      <c r="D6">
+        <v>23.33</v>
+      </c>
+      <c r="E6">
+        <v>33.33</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>36.67</v>
+      </c>
+      <c r="H6">
+        <v>36.67</v>
+      </c>
+      <c r="I6">
+        <v>36.67</v>
+      </c>
+      <c r="J6">
+        <v>33.33</v>
+      </c>
+      <c r="K6">
+        <v>36.67</v>
+      </c>
+      <c r="L6">
+        <v>33.33</v>
+      </c>
+      <c r="M6">
+        <v>30</v>
+      </c>
+      <c r="N6">
+        <v>30</v>
+      </c>
+      <c r="O6">
+        <v>33.33</v>
+      </c>
+      <c r="P6">
+        <v>36.67</v>
+      </c>
+      <c r="Q6">
+        <v>34.67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>53.33</v>
+      </c>
+      <c r="C7">
+        <v>43.33</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>63.33</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <v>60</v>
+      </c>
+      <c r="J7">
+        <v>63.33</v>
+      </c>
+      <c r="K7">
+        <v>73.33</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>66.67</v>
+      </c>
+      <c r="N7">
+        <v>66.67</v>
+      </c>
+      <c r="O7">
+        <v>73.33</v>
+      </c>
+      <c r="P7">
+        <v>70</v>
+      </c>
+      <c r="Q7">
+        <v>60.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>50</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>46.67</v>
+      </c>
+      <c r="E8">
+        <v>56.67</v>
+      </c>
+      <c r="F8">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>63.33</v>
+      </c>
+      <c r="I8">
+        <v>56.67</v>
+      </c>
+      <c r="J8">
+        <v>63.33</v>
+      </c>
+      <c r="K8">
+        <v>66.67</v>
+      </c>
+      <c r="L8">
+        <v>63.33</v>
+      </c>
+      <c r="M8">
+        <v>56.67</v>
+      </c>
+      <c r="N8">
+        <v>56.67</v>
+      </c>
+      <c r="O8">
+        <v>53.33</v>
+      </c>
+      <c r="P8">
+        <v>53.33</v>
+      </c>
+      <c r="Q8">
+        <v>55.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>46.67</v>
+      </c>
+      <c r="C9">
+        <v>36.67</v>
+      </c>
+      <c r="D9">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>53.33</v>
+      </c>
+      <c r="G9">
+        <v>56.67</v>
+      </c>
+      <c r="H9">
+        <v>53.33</v>
+      </c>
+      <c r="I9">
+        <v>53.33</v>
+      </c>
+      <c r="J9">
+        <v>56.67</v>
+      </c>
+      <c r="K9">
+        <v>56.67</v>
+      </c>
+      <c r="L9">
+        <v>53.33</v>
+      </c>
+      <c r="M9">
+        <v>53.33</v>
+      </c>
+      <c r="N9">
+        <v>50</v>
+      </c>
+      <c r="O9">
+        <v>53.33</v>
+      </c>
+      <c r="P9">
+        <v>56.67</v>
+      </c>
+      <c r="Q9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>48.48</v>
+      </c>
+      <c r="C10">
+        <v>45.45</v>
+      </c>
+      <c r="D10">
+        <v>51.52</v>
+      </c>
+      <c r="E10">
+        <v>54.55</v>
+      </c>
+      <c r="F10">
+        <v>54.55</v>
+      </c>
+      <c r="G10">
+        <v>60.61</v>
+      </c>
+      <c r="H10">
+        <v>66.67</v>
+      </c>
+      <c r="I10">
+        <v>66.67</v>
+      </c>
+      <c r="J10">
+        <v>66.67</v>
+      </c>
+      <c r="K10">
+        <v>66.67</v>
+      </c>
+      <c r="L10">
+        <v>63.64</v>
+      </c>
+      <c r="M10">
+        <v>63.64</v>
+      </c>
+      <c r="N10">
+        <v>60.61</v>
+      </c>
+      <c r="O10">
+        <v>60.61</v>
+      </c>
+      <c r="P10">
+        <v>66.67</v>
+      </c>
+      <c r="Q10">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>45.45</v>
+      </c>
+      <c r="C11">
+        <v>45.45</v>
+      </c>
+      <c r="D11">
+        <v>51.52</v>
+      </c>
+      <c r="E11">
+        <v>54.55</v>
+      </c>
+      <c r="F11">
+        <v>45.45</v>
+      </c>
+      <c r="G11">
+        <v>54.55</v>
+      </c>
+      <c r="H11">
+        <v>51.52</v>
+      </c>
+      <c r="I11">
+        <v>42.42</v>
+      </c>
+      <c r="J11">
+        <v>48.48</v>
+      </c>
+      <c r="K11">
+        <v>48.48</v>
+      </c>
+      <c r="L11">
+        <v>51.52</v>
+      </c>
+      <c r="M11">
+        <v>48.48</v>
+      </c>
+      <c r="N11">
+        <v>51.52</v>
+      </c>
+      <c r="O11">
+        <v>51.52</v>
+      </c>
+      <c r="P11">
+        <v>51.52</v>
+      </c>
+      <c r="Q11">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>46.73</v>
+      </c>
+      <c r="C12">
+        <v>44.09</v>
+      </c>
+      <c r="D12">
+        <v>46.3</v>
+      </c>
+      <c r="E12">
+        <v>49.91</v>
+      </c>
+      <c r="F12">
+        <v>51.33</v>
+      </c>
+      <c r="G12">
+        <v>52.52</v>
+      </c>
+      <c r="H12">
+        <v>52.15</v>
+      </c>
+      <c r="I12">
+        <v>52.24</v>
+      </c>
+      <c r="J12">
+        <v>54.51</v>
+      </c>
+      <c r="K12">
+        <v>56.85</v>
+      </c>
+      <c r="L12">
+        <v>55.18</v>
+      </c>
+      <c r="M12">
+        <v>53.21</v>
+      </c>
+      <c r="N12">
+        <v>53.21</v>
+      </c>
+      <c r="O12">
+        <v>55.55</v>
+      </c>
+      <c r="P12">
+        <v>55.82</v>
+      </c>
+      <c r="Q12">
+        <v>51.97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
         <v>40</v>
       </c>
       <c r="C2">
@@ -4609,7 +6541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
